--- a/data/csv_files/demo_data/reykjavik/demo_reykjavik.xlsx
+++ b/data/csv_files/demo_data/reykjavik/demo_reykjavik.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/G_PSYPLAFOR_methlab$/EEGManyLabs/data/csv_files/demo_data/dartmouth/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/G_PSYPLAFOR_methlab$/EEGManyLabs/data/csv_files/demo_data/reykjavik/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C05BE-10C3-B344-BE4E-97564BDA2B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561A1089-06AB-5842-908C-DF558F1B2B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1400" windowWidth="28240" windowHeight="17100" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
+    <workbookView xWindow="1480" yWindow="800" windowWidth="28240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -60,6 +60,27 @@
   </si>
   <si>
     <t>Handedness</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -431,11 +452,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C03222-1F27-AC4C-9C40-659F3B91E4D1}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="3" width="4.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -464,6 +490,786 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
